--- a/Result/profitability/6418.xlsx
+++ b/Result/profitability/6418.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6657,6 +6657,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>262</v>
+      </c>
+      <c r="D50" t="n">
+        <v>206</v>
+      </c>
+      <c r="E50" t="n">
+        <v>56</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="G50" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>7.49%</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>16</v>
+      </c>
+      <c r="K50" t="n">
+        <v>14</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="N50" t="n">
+        <v>20.35125</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X50" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>3.809999999999999</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.2168468981217984</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-0.1899999999999999</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-0.3275862068965516</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>-1.290000000000003</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>-0.05690339655932963</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
